--- a/output/第10期計画_従業員数の重複計上の整理.xlsx
+++ b/output/第10期計画_従業員数の重複計上の整理.xlsx
@@ -618,7 +618,7 @@
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3町からご提供いただいた社会資源一覧（74事業所）は、同一の施設が複数のサービスで登録されている場合、同じ職員がサービスごとに計上されています。供給制約の推定に用いる従業員数をどの単位で数えるかを整理します。令和8年8月25日の進捗確認の打合せでのご指示に対応するものです。</t>
+          <t>3町からご提供いただいた社会資源一覧（74事業所）は、同一の施設が複数のサービスで登録されている場合、同じ職員がサービスごとに計上されています。供給制約の推定に用いる従業員数をどの単位で数えるかを整理します。令和8年8月26日の進捗確認の打合せでのご指示に対応するものです。</t>
         </is>
       </c>
     </row>
